--- a/artfynd/A 39251-2023 artfynd.xlsx
+++ b/artfynd/A 39251-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115462526</v>
+        <v>115462520</v>
       </c>
       <c r="B2" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -795,42 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115462520</v>
+        <v>115462524</v>
       </c>
       <c r="B3" t="n">
-        <v>56171</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -878,12 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
